--- a/data/original/estadoObra.xlsx
+++ b/data/original/estadoObra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpulgarin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10BD13A4-96D9-4AD6-9B7D-4D79776CD18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407C479B-0131-4B2A-8903-B2B1D8A235E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>Sucursal</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Columna2</t>
+  </si>
+  <si>
+    <t>Prueba</t>
   </si>
 </sst>
 </file>
@@ -159,11 +162,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B9" totalsRowShown="0" dataDxfId="0">
-  <autoFilter ref="A1:B9" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B10" totalsRowShown="0" dataDxfId="2">
+  <autoFilter ref="A1:B10" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Columna1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Columna2" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Columna1" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Columna2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -486,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D84575-0FBF-4B16-B624-879771BD1390}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -565,6 +568,14 @@
         <v>9</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/original/estadoObra.xlsx
+++ b/data/original/estadoObra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpulgarin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407C479B-0131-4B2A-8903-B2B1D8A235E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8730B61-EAE5-40A5-94B1-A1457952419B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
+    <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>Sucursal</t>
   </si>
@@ -66,12 +66,6 @@
   </si>
   <si>
     <t>as</t>
-  </si>
-  <si>
-    <t>Columna1</t>
-  </si>
-  <si>
-    <t>Columna2</t>
   </si>
   <si>
     <t>Prueba</t>
@@ -81,10 +75,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -116,14 +117,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -162,11 +184,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B10" totalsRowShown="0" dataDxfId="2">
-  <autoFilter ref="A1:B10" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="3">
+  <autoFilter ref="A1:B9" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Columna1" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Columna2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Sucursal" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Proyecto" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -489,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D84575-0FBF-4B16-B624-879771BD1390}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -497,35 +519,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>11</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -533,7 +555,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -541,12 +563,12 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
@@ -557,23 +579,15 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/original/estadoObra.xlsx
+++ b/data/original/estadoObra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpulgarin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8730B61-EAE5-40A5-94B1-A1457952419B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24609B8F-A92B-49D7-8BD9-D2F31E1D9ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
   <si>
     <t>Sucursal</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Prueba</t>
+  </si>
+  <si>
+    <t>Cali</t>
   </si>
 </sst>
 </file>
@@ -127,18 +130,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -163,6 +154,18 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -184,11 +187,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="3">
-  <autoFilter ref="A1:B9" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B10" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B10" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Sucursal" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Proyecto" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Sucursal" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Proyecto" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -511,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D84575-0FBF-4B16-B624-879771BD1390}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -590,6 +593,14 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/original/estadoObra.xlsx
+++ b/data/original/estadoObra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpulgarin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24609B8F-A92B-49D7-8BD9-D2F31E1D9ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA28AF6-EB3C-46DA-90F6-4BEE7C597862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
   <si>
     <t>Sucursal</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Cali</t>
+  </si>
+  <si>
+    <t>b</t>
   </si>
 </sst>
 </file>
@@ -187,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B10" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="A1:B10" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B11" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B11" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Sucursal" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Proyecto" dataDxfId="0"/>
@@ -514,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D84575-0FBF-4B16-B624-879771BD1390}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -601,6 +604,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/original/estadoObra.xlsx
+++ b/data/original/estadoObra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpulgarin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA28AF6-EB3C-46DA-90F6-4BEE7C597862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E81F043-02DB-4E12-AFE2-34D976765ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>Sucursal</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>b</t>
+  </si>
+  <si>
+    <t>Barranquilla</t>
+  </si>
+  <si>
+    <t>xe</t>
   </si>
 </sst>
 </file>
@@ -190,8 +196,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B11" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="A1:B11" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B12" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B12" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Sucursal" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Proyecto" dataDxfId="0"/>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D84575-0FBF-4B16-B624-879771BD1390}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -612,6 +618,14 @@
         <v>12</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/original/estadoObra.xlsx
+++ b/data/original/estadoObra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpulgarin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E81F043-02DB-4E12-AFE2-34D976765ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5313277F-A8E8-4058-B058-4F00D7F54266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{D076FB45-6D2B-4B94-AF13-899B38C6F57C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Sucursal</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>xe</t>
+  </si>
+  <si>
+    <t>Final</t>
   </si>
 </sst>
 </file>
@@ -196,8 +199,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B12" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="A1:B12" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}" name="Tabla1" displayName="Tabla1" ref="A1:B13" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B13" xr:uid="{580F31E5-7F75-42F8-BB54-EDE6B32DF38D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{EF23A81E-A252-4452-8C75-2D98E0A7DE71}" name="Sucursal" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E923EF26-5300-4315-B0DA-9B214FAFD84B}" name="Proyecto" dataDxfId="0"/>
@@ -523,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D84575-0FBF-4B16-B624-879771BD1390}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -626,6 +629,14 @@
         <v>14</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
